--- a/DBs/nfl/Results/NFL_2021_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2021_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEDB3F93-1E53-422B-B2BD-B16E76666D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB3C395-0B71-4925-9645-EF14E488874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0DADB550-919E-4EAE-B344-1DF648C023EA}"/>
   </bookViews>
@@ -118,12 +118,6 @@
     <t>JAX</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
     <t>KC</t>
   </si>
   <si>
@@ -148,13 +142,7 @@
     <t>NE</t>
   </si>
   <si>
-    <t>STL</t>
-  </si>
-  <si>
     <t>CHI</t>
-  </si>
-  <si>
-    <t>OAK</t>
   </si>
   <si>
     <t>BAL</t>
@@ -176,6 +164,18 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>WFT</t>
   </si>
 </sst>
 </file>
@@ -1645,10 +1645,10 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1677,10 +1677,10 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1741,10 +1741,10 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -2029,10 +2029,10 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
@@ -2061,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -2093,10 +2093,10 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -2125,10 +2125,10 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2160,7 +2160,7 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2189,7 +2189,7 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -2224,7 +2224,7 @@
         <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
@@ -2253,7 +2253,7 @@
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -2285,7 +2285,7 @@
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
         <v>22</v>
@@ -2320,7 +2320,7 @@
         <v>22</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -2349,7 +2349,7 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>30</v>
@@ -2384,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
@@ -2413,7 +2413,7 @@
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -2448,7 +2448,7 @@
         <v>25</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
@@ -2477,7 +2477,7 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
@@ -2512,7 +2512,7 @@
         <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
@@ -2541,7 +2541,7 @@
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -2576,7 +2576,7 @@
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
         <v>14</v>
@@ -2669,7 +2669,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -2704,7 +2704,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G53" t="s">
         <v>14</v>
@@ -2864,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
@@ -2893,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -2989,10 +2989,10 @@
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G62" t="s">
         <v>14</v>
@@ -3021,10 +3021,10 @@
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
@@ -3053,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F64" t="s">
         <v>29</v>
@@ -3088,7 +3088,7 @@
         <v>29</v>
       </c>
       <c r="F65" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3184,7 +3184,7 @@
         <v>17</v>
       </c>
       <c r="F68" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
@@ -3213,7 +3213,7 @@
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
@@ -3248,7 +3248,7 @@
         <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G70" t="s">
         <v>14</v>
@@ -3277,7 +3277,7 @@
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F71" t="s">
         <v>19</v>
@@ -3309,10 +3309,10 @@
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
         <v>14</v>
@@ -3341,10 +3341,10 @@
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
@@ -3565,7 +3565,7 @@
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F80" t="s">
         <v>29</v>
@@ -3600,7 +3600,7 @@
         <v>29</v>
       </c>
       <c r="F81" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G81" t="s">
         <v>14</v>
@@ -3629,10 +3629,10 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" t="s">
         <v>32</v>
-      </c>
-      <c r="F82" t="s">
-        <v>34</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
@@ -3661,10 +3661,10 @@
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G83" t="s">
         <v>14</v>
@@ -3693,10 +3693,10 @@
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
@@ -3725,10 +3725,10 @@
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F85" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
@@ -3757,7 +3757,7 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F86" t="s">
         <v>21</v>
@@ -3792,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
@@ -3821,10 +3821,10 @@
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F88" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
@@ -3853,10 +3853,10 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F89" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
@@ -3949,7 +3949,7 @@
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
@@ -3984,7 +3984,7 @@
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
@@ -4013,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -4048,7 +4048,7 @@
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G95" t="s">
         <v>14</v>
@@ -4205,7 +4205,7 @@
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F100" t="s">
         <v>17</v>
@@ -4240,7 +4240,7 @@
         <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G101" t="s">
         <v>14</v>
@@ -4397,7 +4397,7 @@
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F106" t="s">
         <v>29</v>
@@ -4432,7 +4432,7 @@
         <v>29</v>
       </c>
       <c r="F107" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
@@ -4461,7 +4461,7 @@
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F108" t="s">
         <v>23</v>
@@ -4496,7 +4496,7 @@
         <v>23</v>
       </c>
       <c r="F109" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G109" t="s">
         <v>14</v>
@@ -4528,7 +4528,7 @@
         <v>25</v>
       </c>
       <c r="F110" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
@@ -4557,7 +4557,7 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F111" t="s">
         <v>25</v>
@@ -4589,7 +4589,7 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
@@ -4624,7 +4624,7 @@
         <v>16</v>
       </c>
       <c r="F113" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G113" t="s">
         <v>14</v>
@@ -4653,10 +4653,10 @@
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
@@ -4685,10 +4685,10 @@
         <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F115" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G115" t="s">
         <v>14</v>
@@ -4784,7 +4784,7 @@
         <v>26</v>
       </c>
       <c r="F118" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
@@ -4813,7 +4813,7 @@
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F119" t="s">
         <v>26</v>
@@ -4909,10 +4909,10 @@
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F122" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
@@ -4941,10 +4941,10 @@
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F123" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
         <v>14</v>
@@ -4973,7 +4973,7 @@
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F124" t="s">
         <v>18</v>
@@ -5008,7 +5008,7 @@
         <v>18</v>
       </c>
       <c r="F125" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
@@ -5040,7 +5040,7 @@
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
@@ -5069,7 +5069,7 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F127" t="s">
         <v>12</v>
@@ -5101,10 +5101,10 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F128" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G128" t="s">
         <v>14</v>
@@ -5133,10 +5133,10 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F129" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F130" t="s">
         <v>24</v>
@@ -5200,7 +5200,7 @@
         <v>24</v>
       </c>
       <c r="F131" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G131" t="s">
         <v>14</v>
@@ -5357,7 +5357,7 @@
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F136" t="s">
         <v>22</v>
@@ -5392,7 +5392,7 @@
         <v>22</v>
       </c>
       <c r="F137" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G137" t="s">
         <v>14</v>
@@ -5424,7 +5424,7 @@
         <v>18</v>
       </c>
       <c r="F138" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G138" t="s">
         <v>14</v>
@@ -5453,7 +5453,7 @@
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F139" t="s">
         <v>18</v>
@@ -5549,7 +5549,7 @@
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F142" t="s">
         <v>30</v>
@@ -5584,7 +5584,7 @@
         <v>30</v>
       </c>
       <c r="F143" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G143" t="s">
         <v>14</v>
@@ -5680,7 +5680,7 @@
         <v>12</v>
       </c>
       <c r="F146" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G146" t="s">
         <v>14</v>
@@ -5709,7 +5709,7 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F147" t="s">
         <v>12</v>
@@ -5741,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F148" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
@@ -5773,10 +5773,10 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F149" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G149" t="s">
         <v>14</v>
@@ -5805,10 +5805,10 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F150" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
@@ -5837,10 +5837,10 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F151" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G151" t="s">
         <v>14</v>
@@ -5869,10 +5869,10 @@
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F152" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G152" t="s">
         <v>14</v>
@@ -5901,10 +5901,10 @@
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F153" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
@@ -6000,7 +6000,7 @@
         <v>13</v>
       </c>
       <c r="F156" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G156" t="s">
         <v>14</v>
@@ -6029,7 +6029,7 @@
         <v>11</v>
       </c>
       <c r="E157" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F157" t="s">
         <v>13</v>
@@ -6064,7 +6064,7 @@
         <v>19</v>
       </c>
       <c r="F158" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
@@ -6093,7 +6093,7 @@
         <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F159" t="s">
         <v>19</v>
@@ -6125,7 +6125,7 @@
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F160" t="s">
         <v>25</v>
@@ -6160,7 +6160,7 @@
         <v>25</v>
       </c>
       <c r="F161" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
@@ -6256,7 +6256,7 @@
         <v>31</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G164" t="s">
         <v>14</v>
@@ -6285,7 +6285,7 @@
         <v>11</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -6381,10 +6381,10 @@
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F168" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G168" t="s">
         <v>15</v>
@@ -6413,10 +6413,10 @@
         <v>11</v>
       </c>
       <c r="E169" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F169" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G169" t="s">
         <v>14</v>
@@ -6573,10 +6573,10 @@
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F174" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G174" t="s">
         <v>15</v>
@@ -6605,10 +6605,10 @@
         <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F175" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G175" t="s">
         <v>14</v>
@@ -6637,10 +6637,10 @@
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F176" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
@@ -6669,10 +6669,10 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G177" t="s">
         <v>14</v>
@@ -6701,10 +6701,10 @@
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F178" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G178" t="s">
         <v>14</v>
@@ -6733,10 +6733,10 @@
         <v>11</v>
       </c>
       <c r="E179" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F179" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
@@ -6768,7 +6768,7 @@
         <v>26</v>
       </c>
       <c r="F180" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
@@ -6797,7 +6797,7 @@
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F181" t="s">
         <v>26</v>
@@ -6832,7 +6832,7 @@
         <v>13</v>
       </c>
       <c r="F182" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
@@ -6861,7 +6861,7 @@
         <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F183" t="s">
         <v>13</v>
@@ -6893,10 +6893,10 @@
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F184" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
@@ -6925,10 +6925,10 @@
         <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F185" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G185" t="s">
         <v>14</v>
@@ -7085,10 +7085,10 @@
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F190" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G190" t="s">
         <v>14</v>
@@ -7117,10 +7117,10 @@
         <v>11</v>
       </c>
       <c r="E191" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F191" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G191" t="s">
         <v>15</v>
@@ -7152,7 +7152,7 @@
         <v>17</v>
       </c>
       <c r="F192" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G192" t="s">
         <v>15</v>
@@ -7181,7 +7181,7 @@
         <v>11</v>
       </c>
       <c r="E193" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F193" t="s">
         <v>17</v>
@@ -7213,7 +7213,7 @@
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F194" t="s">
         <v>20</v>
@@ -7248,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="F195" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G195" t="s">
         <v>15</v>
@@ -7280,7 +7280,7 @@
         <v>22</v>
       </c>
       <c r="F196" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
@@ -7309,7 +7309,7 @@
         <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F197" t="s">
         <v>22</v>
@@ -7341,10 +7341,10 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F198" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G198" t="s">
         <v>14</v>
@@ -7373,10 +7373,10 @@
         <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F199" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G199" t="s">
         <v>15</v>
@@ -7408,7 +7408,7 @@
         <v>27</v>
       </c>
       <c r="F200" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G200" t="s">
         <v>14</v>
@@ -7437,7 +7437,7 @@
         <v>11</v>
       </c>
       <c r="E201" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F201" t="s">
         <v>27</v>
@@ -7469,7 +7469,7 @@
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F202" t="s">
         <v>21</v>
@@ -7504,7 +7504,7 @@
         <v>21</v>
       </c>
       <c r="F203" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G203" t="s">
         <v>15</v>
@@ -7533,7 +7533,7 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F204" t="s">
         <v>29</v>
@@ -7568,7 +7568,7 @@
         <v>29</v>
       </c>
       <c r="F205" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G205" t="s">
         <v>15</v>
@@ -7597,7 +7597,7 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F206" t="s">
         <v>16</v>
@@ -7632,7 +7632,7 @@
         <v>16</v>
       </c>
       <c r="F207" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G207" t="s">
         <v>15</v>
@@ -7664,7 +7664,7 @@
         <v>12</v>
       </c>
       <c r="F208" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G208" t="s">
         <v>14</v>
@@ -7693,7 +7693,7 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F209" t="s">
         <v>12</v>
@@ -7853,7 +7853,7 @@
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F214" t="s">
         <v>24</v>
@@ -7888,7 +7888,7 @@
         <v>24</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G215" t="s">
         <v>14</v>
@@ -7917,7 +7917,7 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F216" t="s">
         <v>26</v>
@@ -7952,7 +7952,7 @@
         <v>26</v>
       </c>
       <c r="F217" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G217" t="s">
         <v>14</v>
@@ -8048,7 +8048,7 @@
         <v>19</v>
       </c>
       <c r="F220" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G220" t="s">
         <v>14</v>
@@ -8077,7 +8077,7 @@
         <v>11</v>
       </c>
       <c r="E221" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F221" t="s">
         <v>19</v>
@@ -8112,7 +8112,7 @@
         <v>28</v>
       </c>
       <c r="F222" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G222" t="s">
         <v>15</v>
@@ -8141,7 +8141,7 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -8240,7 +8240,7 @@
         <v>18</v>
       </c>
       <c r="F226" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G226" t="s">
         <v>15</v>
@@ -8269,7 +8269,7 @@
         <v>11</v>
       </c>
       <c r="E227" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F227" t="s">
         <v>18</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F232" t="s">
         <v>30</v>
@@ -8464,7 +8464,7 @@
         <v>30</v>
       </c>
       <c r="F233" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G233" t="s">
         <v>14</v>
@@ -8557,10 +8557,10 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F236" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G236" t="s">
         <v>15</v>
@@ -8589,10 +8589,10 @@
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F237" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G237" t="s">
         <v>14</v>
@@ -8621,7 +8621,7 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F238" t="s">
         <v>12</v>
@@ -8656,7 +8656,7 @@
         <v>12</v>
       </c>
       <c r="F239" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
         <v>15</v>
@@ -8685,10 +8685,10 @@
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F240" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G240" t="s">
         <v>14</v>
@@ -8717,10 +8717,10 @@
         <v>11</v>
       </c>
       <c r="E241" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F241" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G241" t="s">
         <v>15</v>
@@ -8813,10 +8813,10 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F244" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G244" t="s">
         <v>14</v>
@@ -8845,10 +8845,10 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F245" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G245" t="s">
         <v>15</v>
@@ -8944,7 +8944,7 @@
         <v>17</v>
       </c>
       <c r="F248" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G248" t="s">
         <v>15</v>
@@ -8973,7 +8973,7 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F249" t="s">
         <v>17</v>
@@ -9069,7 +9069,7 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F252" t="s">
         <v>13</v>
@@ -9104,7 +9104,7 @@
         <v>13</v>
       </c>
       <c r="F253" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G253" t="s">
         <v>14</v>
@@ -9133,7 +9133,7 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F254" t="s">
         <v>23</v>
@@ -9168,7 +9168,7 @@
         <v>23</v>
       </c>
       <c r="F255" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G255" t="s">
         <v>15</v>
@@ -9197,7 +9197,7 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F256" t="s">
         <v>20</v>
@@ -9232,7 +9232,7 @@
         <v>20</v>
       </c>
       <c r="F257" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G257" t="s">
         <v>14</v>
@@ -9261,7 +9261,7 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F258" t="s">
         <v>22</v>
@@ -9296,7 +9296,7 @@
         <v>22</v>
       </c>
       <c r="F259" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G259" t="s">
         <v>14</v>
@@ -9325,7 +9325,7 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F260" t="s">
         <v>30</v>
@@ -9360,7 +9360,7 @@
         <v>30</v>
       </c>
       <c r="F261" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G261" t="s">
         <v>15</v>
@@ -9389,10 +9389,10 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F262" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G262" t="s">
         <v>14</v>
@@ -9421,10 +9421,10 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F263" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G263" t="s">
         <v>15</v>
@@ -9453,7 +9453,7 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F264" t="s">
         <v>16</v>
@@ -9488,7 +9488,7 @@
         <v>16</v>
       </c>
       <c r="F265" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G265" t="s">
         <v>14</v>
@@ -9581,10 +9581,10 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F268" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G268" t="s">
         <v>14</v>
@@ -9613,10 +9613,10 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F269" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G269" t="s">
         <v>15</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="F270" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G270" t="s">
         <v>15</v>
@@ -9677,7 +9677,7 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F271" t="s">
         <v>27</v>
@@ -9712,7 +9712,7 @@
         <v>18</v>
       </c>
       <c r="F272" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G272" t="s">
         <v>14</v>
@@ -9741,7 +9741,7 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F273" t="s">
         <v>18</v>
@@ -9773,10 +9773,10 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F274" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G274" t="s">
         <v>14</v>
@@ -9805,10 +9805,10 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F275" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G275" t="s">
         <v>15</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="F282" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G282" t="s">
         <v>14</v>
@@ -10061,7 +10061,7 @@
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F283" t="s">
         <v>27</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F284" t="s">
         <v>12</v>
@@ -10128,7 +10128,7 @@
         <v>12</v>
       </c>
       <c r="F285" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G285" t="s">
         <v>15</v>
@@ -10157,10 +10157,10 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F286" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G286" t="s">
         <v>14</v>
@@ -10189,10 +10189,10 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F287" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G287" t="s">
         <v>15</v>
@@ -10288,7 +10288,7 @@
         <v>23</v>
       </c>
       <c r="F290" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G290" t="s">
         <v>15</v>
@@ -10317,7 +10317,7 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>23</v>
@@ -10416,7 +10416,7 @@
         <v>16</v>
       </c>
       <c r="F294" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G294" t="s">
         <v>15</v>
@@ -10445,7 +10445,7 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F295" t="s">
         <v>16</v>
@@ -10477,7 +10477,7 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F296" t="s">
         <v>24</v>
@@ -10512,7 +10512,7 @@
         <v>24</v>
       </c>
       <c r="F297" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G297" t="s">
         <v>15</v>
@@ -10541,10 +10541,10 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F298" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G298" t="s">
         <v>15</v>
@@ -10573,10 +10573,10 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F299" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G299" t="s">
         <v>14</v>
@@ -10608,7 +10608,7 @@
         <v>28</v>
       </c>
       <c r="F300" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G300" t="s">
         <v>14</v>
@@ -10637,7 +10637,7 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -10669,7 +10669,7 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F302" t="s">
         <v>17</v>
@@ -10704,7 +10704,7 @@
         <v>17</v>
       </c>
       <c r="F303" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G303" t="s">
         <v>14</v>
@@ -10797,10 +10797,10 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F306" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G306" t="s">
         <v>15</v>
@@ -10829,10 +10829,10 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F307" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G307" t="s">
         <v>14</v>
@@ -10992,7 +10992,7 @@
         <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G312" t="s">
         <v>14</v>
@@ -11021,7 +11021,7 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F313" t="s">
         <v>16</v>
@@ -11053,7 +11053,7 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F314" t="s">
         <v>20</v>
@@ -11088,7 +11088,7 @@
         <v>20</v>
       </c>
       <c r="F315" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G315" t="s">
         <v>14</v>
@@ -11117,7 +11117,7 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F316" t="s">
         <v>29</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="F317" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G317" t="s">
         <v>15</v>
@@ -11184,7 +11184,7 @@
         <v>23</v>
       </c>
       <c r="F318" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G318" t="s">
         <v>14</v>
@@ -11213,7 +11213,7 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F319" t="s">
         <v>23</v>
@@ -11245,7 +11245,7 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F320" t="s">
         <v>21</v>
@@ -11280,7 +11280,7 @@
         <v>21</v>
       </c>
       <c r="F321" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G321" t="s">
         <v>14</v>
@@ -11312,7 +11312,7 @@
         <v>22</v>
       </c>
       <c r="F322" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G322" t="s">
         <v>15</v>
@@ -11341,7 +11341,7 @@
         <v>11</v>
       </c>
       <c r="E323" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F323" t="s">
         <v>22</v>
@@ -11373,7 +11373,7 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F324" t="s">
         <v>13</v>
@@ -11408,7 +11408,7 @@
         <v>13</v>
       </c>
       <c r="F325" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G325" t="s">
         <v>15</v>
@@ -11501,7 +11501,7 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F328" t="s">
         <v>18</v>
@@ -11536,7 +11536,7 @@
         <v>18</v>
       </c>
       <c r="F329" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G329" t="s">
         <v>15</v>
@@ -11568,7 +11568,7 @@
         <v>12</v>
       </c>
       <c r="F330" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G330" t="s">
         <v>14</v>
@@ -11597,7 +11597,7 @@
         <v>11</v>
       </c>
       <c r="E331" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F331" t="s">
         <v>12</v>
@@ -11629,7 +11629,7 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F332" t="s">
         <v>29</v>
@@ -11664,7 +11664,7 @@
         <v>29</v>
       </c>
       <c r="F333" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G333" t="s">
         <v>14</v>
@@ -11693,7 +11693,7 @@
         <v>11</v>
       </c>
       <c r="E334" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F334" t="s">
         <v>13</v>
@@ -11728,7 +11728,7 @@
         <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G335" t="s">
         <v>14</v>
@@ -11760,7 +11760,7 @@
         <v>19</v>
       </c>
       <c r="F336" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G336" t="s">
         <v>15</v>
@@ -11789,7 +11789,7 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F337" t="s">
         <v>19</v>
@@ -12013,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F344" t="s">
         <v>16</v>
@@ -12048,7 +12048,7 @@
         <v>16</v>
       </c>
       <c r="F345" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G345" t="s">
         <v>15</v>
@@ -12077,7 +12077,7 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F346" t="s">
         <v>20</v>
@@ -12112,7 +12112,7 @@
         <v>20</v>
       </c>
       <c r="F347" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G347" t="s">
         <v>15</v>
@@ -12205,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F350" t="s">
         <v>27</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="F351" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G351" t="s">
         <v>15</v>
@@ -12269,10 +12269,10 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F352" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G352" t="s">
         <v>14</v>
@@ -12301,10 +12301,10 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F353" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G353" t="s">
         <v>15</v>
@@ -12397,10 +12397,10 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F356" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G356" t="s">
         <v>14</v>
@@ -12429,10 +12429,10 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F357" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G357" t="s">
         <v>15</v>
@@ -12461,10 +12461,10 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F358" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G358" t="s">
         <v>14</v>
@@ -12493,10 +12493,10 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F359" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G359" t="s">
         <v>15</v>
@@ -12525,7 +12525,7 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F360" t="s">
         <v>24</v>
@@ -12560,7 +12560,7 @@
         <v>24</v>
       </c>
       <c r="F361" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G361" t="s">
         <v>15</v>
@@ -12592,7 +12592,7 @@
         <v>13</v>
       </c>
       <c r="F362" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G362" t="s">
         <v>15</v>
@@ -12621,7 +12621,7 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F363" t="s">
         <v>13</v>
@@ -12720,7 +12720,7 @@
         <v>26</v>
       </c>
       <c r="F366" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G366" t="s">
         <v>15</v>
@@ -12749,7 +12749,7 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F367" t="s">
         <v>26</v>
@@ -12781,7 +12781,7 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F368" t="s">
         <v>22</v>
@@ -12816,7 +12816,7 @@
         <v>22</v>
       </c>
       <c r="F369" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G369" t="s">
         <v>14</v>
@@ -13037,10 +13037,10 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F376" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G376" t="s">
         <v>14</v>
@@ -13069,10 +13069,10 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F377" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G377" t="s">
         <v>15</v>
@@ -13165,10 +13165,10 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F380" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G380" t="s">
         <v>15</v>
@@ -13197,10 +13197,10 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F381" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G381" t="s">
         <v>14</v>
@@ -13229,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F382" t="s">
         <v>31</v>
@@ -13264,7 +13264,7 @@
         <v>31</v>
       </c>
       <c r="F383" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G383" t="s">
         <v>15</v>
@@ -13296,7 +13296,7 @@
         <v>18</v>
       </c>
       <c r="F384" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G384" t="s">
         <v>14</v>
@@ -13325,7 +13325,7 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F385" t="s">
         <v>18</v>
@@ -13357,10 +13357,10 @@
         <v>11</v>
       </c>
       <c r="E386" t="s">
+        <v>32</v>
+      </c>
+      <c r="F386" t="s">
         <v>34</v>
-      </c>
-      <c r="F386" t="s">
-        <v>36</v>
       </c>
       <c r="G386" t="s">
         <v>14</v>
@@ -13389,10 +13389,10 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F387" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G387" t="s">
         <v>15</v>
@@ -13421,7 +13421,7 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F388" t="s">
         <v>19</v>
@@ -13456,7 +13456,7 @@
         <v>19</v>
       </c>
       <c r="F389" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G389" t="s">
         <v>14</v>
@@ -13677,10 +13677,10 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F396" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G396" t="s">
         <v>14</v>
@@ -13709,10 +13709,10 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F397" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G397" t="s">
         <v>15</v>
@@ -13744,7 +13744,7 @@
         <v>13</v>
       </c>
       <c r="F398" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G398" t="s">
         <v>15</v>
@@ -13773,7 +13773,7 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F399" t="s">
         <v>13</v>
@@ -13933,10 +13933,10 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F404" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G404" t="s">
         <v>14</v>
@@ -13965,10 +13965,10 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F405" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G405" t="s">
         <v>15</v>
@@ -13997,7 +13997,7 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F406" t="s">
         <v>21</v>
@@ -14032,7 +14032,7 @@
         <v>21</v>
       </c>
       <c r="F407" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G407" t="s">
         <v>14</v>
@@ -14061,7 +14061,7 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F408" t="s">
         <v>29</v>
@@ -14096,7 +14096,7 @@
         <v>29</v>
       </c>
       <c r="F409" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G409" t="s">
         <v>15</v>
@@ -14125,10 +14125,10 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F410" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G410" t="s">
         <v>14</v>
@@ -14157,10 +14157,10 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F411" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G411" t="s">
         <v>15</v>
@@ -14253,10 +14253,10 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F414" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G414" t="s">
         <v>14</v>
@@ -14285,10 +14285,10 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F415" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G415" t="s">
         <v>15</v>
@@ -14317,7 +14317,7 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F416" t="s">
         <v>26</v>
@@ -14352,7 +14352,7 @@
         <v>26</v>
       </c>
       <c r="F417" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
@@ -14381,10 +14381,10 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F418" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G418" t="s">
         <v>15</v>
@@ -14413,10 +14413,10 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
+        <v>49</v>
+      </c>
+      <c r="F419" t="s">
         <v>32</v>
-      </c>
-      <c r="F419" t="s">
-        <v>34</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
@@ -14448,7 +14448,7 @@
         <v>25</v>
       </c>
       <c r="F420" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G420" t="s">
         <v>14</v>
@@ -14477,7 +14477,7 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F421" t="s">
         <v>25</v>
@@ -14640,7 +14640,7 @@
         <v>13</v>
       </c>
       <c r="F426" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G426" t="s">
         <v>15</v>
@@ -14669,7 +14669,7 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F427" t="s">
         <v>13</v>
@@ -14701,10 +14701,10 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F428" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G428" t="s">
         <v>15</v>
@@ -14733,10 +14733,10 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F429" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G429" t="s">
         <v>14</v>
@@ -14829,7 +14829,7 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F432" t="s">
         <v>21</v>
@@ -14864,7 +14864,7 @@
         <v>21</v>
       </c>
       <c r="F433" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G433" t="s">
         <v>15</v>
@@ -15024,7 +15024,7 @@
         <v>22</v>
       </c>
       <c r="F438" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G438" t="s">
         <v>15</v>
@@ -15053,7 +15053,7 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F439" t="s">
         <v>22</v>
@@ -15085,7 +15085,7 @@
         <v>11</v>
       </c>
       <c r="E440" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F440" t="s">
         <v>12</v>
@@ -15120,7 +15120,7 @@
         <v>12</v>
       </c>
       <c r="F441" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G441" t="s">
         <v>14</v>
@@ -15149,10 +15149,10 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F442" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G442" t="s">
         <v>15</v>
@@ -15181,10 +15181,10 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F443" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G443" t="s">
         <v>14</v>
@@ -15216,7 +15216,7 @@
         <v>23</v>
       </c>
       <c r="F444" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G444" t="s">
         <v>15</v>
@@ -15245,7 +15245,7 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F445" t="s">
         <v>23</v>
@@ -15280,7 +15280,7 @@
         <v>16</v>
       </c>
       <c r="F446" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G446" t="s">
         <v>14</v>
@@ -15309,7 +15309,7 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F447" t="s">
         <v>16</v>
@@ -15341,7 +15341,7 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F448" t="s">
         <v>24</v>
@@ -15376,7 +15376,7 @@
         <v>24</v>
       </c>
       <c r="F449" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G449" t="s">
         <v>15</v>
@@ -15469,10 +15469,10 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F452" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G452" t="s">
         <v>14</v>
@@ -15501,10 +15501,10 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F453" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G453" t="s">
         <v>15</v>
@@ -15664,7 +15664,7 @@
         <v>19</v>
       </c>
       <c r="F458" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G458" t="s">
         <v>15</v>
@@ -15693,7 +15693,7 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F459" t="s">
         <v>19</v>
@@ -15792,7 +15792,7 @@
         <v>22</v>
       </c>
       <c r="F462" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G462" t="s">
         <v>14</v>
@@ -15821,7 +15821,7 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>22</v>
@@ -15856,7 +15856,7 @@
         <v>30</v>
       </c>
       <c r="F464" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G464" t="s">
         <v>14</v>
@@ -15885,7 +15885,7 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F465" t="s">
         <v>30</v>
@@ -15981,7 +15981,7 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F468" t="s">
         <v>23</v>
@@ -16016,7 +16016,7 @@
         <v>23</v>
       </c>
       <c r="F469" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G469" t="s">
         <v>14</v>
@@ -16048,7 +16048,7 @@
         <v>16</v>
       </c>
       <c r="F470" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G470" t="s">
         <v>14</v>
@@ -16077,7 +16077,7 @@
         <v>11</v>
       </c>
       <c r="E471" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F471" t="s">
         <v>16</v>
@@ -16109,7 +16109,7 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>24</v>
@@ -16144,7 +16144,7 @@
         <v>24</v>
       </c>
       <c r="F473" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
@@ -16173,10 +16173,10 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F474" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G474" t="s">
         <v>14</v>
@@ -16205,10 +16205,10 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F475" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G475" t="s">
         <v>15</v>
@@ -16237,7 +16237,7 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F476" t="s">
         <v>18</v>
@@ -16272,7 +16272,7 @@
         <v>18</v>
       </c>
       <c r="F477" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G477" t="s">
         <v>15</v>
@@ -16304,7 +16304,7 @@
         <v>13</v>
       </c>
       <c r="F478" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G478" t="s">
         <v>14</v>
@@ -16333,7 +16333,7 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F479" t="s">
         <v>13</v>
@@ -16365,10 +16365,10 @@
         <v>11</v>
       </c>
       <c r="E480" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F480" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G480" t="s">
         <v>15</v>
@@ -16397,10 +16397,10 @@
         <v>11</v>
       </c>
       <c r="E481" t="s">
+        <v>36</v>
+      </c>
+      <c r="F481" t="s">
         <v>38</v>
-      </c>
-      <c r="F481" t="s">
-        <v>40</v>
       </c>
       <c r="G481" t="s">
         <v>14</v>
@@ -16493,7 +16493,7 @@
         <v>11</v>
       </c>
       <c r="E484" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>20</v>
@@ -16528,7 +16528,7 @@
         <v>20</v>
       </c>
       <c r="F485" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G485" t="s">
         <v>15</v>
@@ -16557,10 +16557,10 @@
         <v>11</v>
       </c>
       <c r="E486" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F486" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G486" t="s">
         <v>14</v>
@@ -16589,10 +16589,10 @@
         <v>11</v>
       </c>
       <c r="E487" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G487" t="s">
         <v>15</v>
@@ -16624,7 +16624,7 @@
         <v>22</v>
       </c>
       <c r="F488" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G488" t="s">
         <v>14</v>
@@ -16653,7 +16653,7 @@
         <v>11</v>
       </c>
       <c r="E489" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F489" t="s">
         <v>22</v>
@@ -16685,7 +16685,7 @@
         <v>11</v>
       </c>
       <c r="E490" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F490" t="s">
         <v>25</v>
@@ -16720,7 +16720,7 @@
         <v>25</v>
       </c>
       <c r="F491" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G491" t="s">
         <v>14</v>
@@ -16749,7 +16749,7 @@
         <v>11</v>
       </c>
       <c r="E492" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F492" t="s">
         <v>31</v>
@@ -16784,7 +16784,7 @@
         <v>31</v>
       </c>
       <c r="F493" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G493" t="s">
         <v>15</v>
@@ -16816,7 +16816,7 @@
         <v>27</v>
       </c>
       <c r="F494" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
@@ -16845,7 +16845,7 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F495" t="s">
         <v>27</v>
@@ -16944,7 +16944,7 @@
         <v>16</v>
       </c>
       <c r="F498" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G498" t="s">
         <v>15</v>
@@ -16973,7 +16973,7 @@
         <v>11</v>
       </c>
       <c r="E499" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F499" t="s">
         <v>16</v>
@@ -17005,10 +17005,10 @@
         <v>11</v>
       </c>
       <c r="E500" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F500" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
@@ -17037,10 +17037,10 @@
         <v>11</v>
       </c>
       <c r="E501" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G501" t="s">
         <v>15</v>
@@ -17261,10 +17261,10 @@
         <v>11</v>
       </c>
       <c r="E508" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F508" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G508" t="s">
         <v>15</v>
@@ -17293,10 +17293,10 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F509" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G509" t="s">
         <v>14</v>
@@ -17325,7 +17325,7 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F510" t="s">
         <v>23</v>
@@ -17360,7 +17360,7 @@
         <v>23</v>
       </c>
       <c r="F511" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G511" t="s">
         <v>15</v>
@@ -17392,7 +17392,7 @@
         <v>18</v>
       </c>
       <c r="F512" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
@@ -17421,7 +17421,7 @@
         <v>11</v>
       </c>
       <c r="E513" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F513" t="s">
         <v>18</v>
@@ -17453,10 +17453,10 @@
         <v>11</v>
       </c>
       <c r="E514" t="s">
+        <v>32</v>
+      </c>
+      <c r="F514" t="s">
         <v>34</v>
-      </c>
-      <c r="F514" t="s">
-        <v>36</v>
       </c>
       <c r="G514" t="s">
         <v>15</v>
@@ -17485,10 +17485,10 @@
         <v>11</v>
       </c>
       <c r="E515" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F515" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G515" t="s">
         <v>14</v>
@@ -17581,7 +17581,7 @@
         <v>11</v>
       </c>
       <c r="E518" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F518" t="s">
         <v>17</v>
@@ -17616,7 +17616,7 @@
         <v>17</v>
       </c>
       <c r="F519" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G519" t="s">
         <v>14</v>
@@ -17712,7 +17712,7 @@
         <v>23</v>
       </c>
       <c r="F522" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
@@ -17741,7 +17741,7 @@
         <v>11</v>
       </c>
       <c r="E523" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F523" t="s">
         <v>23</v>
@@ -17773,7 +17773,7 @@
         <v>11</v>
       </c>
       <c r="E524" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F524" t="s">
         <v>22</v>
@@ -17808,7 +17808,7 @@
         <v>22</v>
       </c>
       <c r="F525" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G525" t="s">
         <v>15</v>
@@ -17904,7 +17904,7 @@
         <v>29</v>
       </c>
       <c r="F528" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
@@ -17933,7 +17933,7 @@
         <v>11</v>
       </c>
       <c r="E529" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F529" t="s">
         <v>29</v>
@@ -18029,10 +18029,10 @@
         <v>11</v>
       </c>
       <c r="E532" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F532" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
@@ -18061,10 +18061,10 @@
         <v>11</v>
       </c>
       <c r="E533" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F533" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G533" t="s">
         <v>15</v>
@@ -18093,10 +18093,10 @@
         <v>11</v>
       </c>
       <c r="E534" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F534" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G534" t="s">
         <v>15</v>
@@ -18125,10 +18125,10 @@
         <v>11</v>
       </c>
       <c r="E535" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F535" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G535" t="s">
         <v>14</v>
@@ -18160,7 +18160,7 @@
         <v>18</v>
       </c>
       <c r="F536" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G536" t="s">
         <v>15</v>
@@ -18189,7 +18189,7 @@
         <v>11</v>
       </c>
       <c r="E537" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F537" t="s">
         <v>18</v>
@@ -18352,7 +18352,7 @@
         <v>28</v>
       </c>
       <c r="F542" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G542" t="s">
         <v>15</v>
@@ -18381,7 +18381,7 @@
         <v>11</v>
       </c>
       <c r="E543" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F543" t="s">
         <v>28</v>
@@ -18413,10 +18413,10 @@
         <v>11</v>
       </c>
       <c r="E544" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F544" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
@@ -18445,10 +18445,10 @@
         <v>11</v>
       </c>
       <c r="E545" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F545" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G545" t="s">
         <v>15</v>
@@ -18471,16 +18471,16 @@
         <v>2021</v>
       </c>
       <c r="C546" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D546" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E546" t="s">
         <v>22</v>
       </c>
       <c r="F546" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G546" t="s">
         <v>14</v>
@@ -18503,13 +18503,13 @@
         <v>2021</v>
       </c>
       <c r="C547" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D547" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E547" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F547" t="s">
         <v>22</v>
@@ -18535,16 +18535,16 @@
         <v>2021</v>
       </c>
       <c r="C548" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D548" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E548" t="s">
         <v>19</v>
       </c>
       <c r="F548" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G548" t="s">
         <v>14</v>
@@ -18567,13 +18567,13 @@
         <v>2021</v>
       </c>
       <c r="C549" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D549" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E549" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F549" t="s">
         <v>19</v>
@@ -18599,10 +18599,10 @@
         <v>2021</v>
       </c>
       <c r="C550" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D550" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E550" t="s">
         <v>12</v>
@@ -18631,10 +18631,10 @@
         <v>2021</v>
       </c>
       <c r="C551" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D551" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E551" t="s">
         <v>16</v>
@@ -18663,10 +18663,10 @@
         <v>2021</v>
       </c>
       <c r="C552" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D552" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -18695,10 +18695,10 @@
         <v>2021</v>
       </c>
       <c r="C553" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D553" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E553" t="s">
         <v>13</v>
@@ -18727,13 +18727,13 @@
         <v>2021</v>
       </c>
       <c r="C554" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D554" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E554" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F554" t="s">
         <v>18</v>
@@ -18759,16 +18759,16 @@
         <v>2021</v>
       </c>
       <c r="C555" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D555" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E555" t="s">
         <v>18</v>
       </c>
       <c r="F555" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G555" t="s">
         <v>15</v>
@@ -18791,13 +18791,13 @@
         <v>2021</v>
       </c>
       <c r="C556" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D556" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E556" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F556" t="s">
         <v>26</v>
@@ -18823,16 +18823,16 @@
         <v>2021</v>
       </c>
       <c r="C557" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D557" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E557" t="s">
         <v>26</v>
       </c>
       <c r="F557" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G557" t="s">
         <v>15</v>
@@ -18855,10 +18855,10 @@
         <v>2021</v>
       </c>
       <c r="C558" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D558" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E558" t="s">
         <v>22</v>
@@ -18887,10 +18887,10 @@
         <v>2021</v>
       </c>
       <c r="C559" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D559" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E559" t="s">
         <v>27</v>
@@ -18919,16 +18919,16 @@
         <v>2021</v>
       </c>
       <c r="C560" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D560" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
       </c>
       <c r="F560" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G560" t="s">
         <v>15</v>
@@ -18951,13 +18951,13 @@
         <v>2021</v>
       </c>
       <c r="C561" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D561" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E561" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F561" t="s">
         <v>28</v>
@@ -18983,13 +18983,13 @@
         <v>2021</v>
       </c>
       <c r="C562" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D562" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E562" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F562" t="s">
         <v>12</v>
@@ -19015,16 +19015,16 @@
         <v>2021</v>
       </c>
       <c r="C563" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D563" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E563" t="s">
         <v>12</v>
       </c>
       <c r="F563" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G563" t="s">
         <v>14</v>
@@ -19047,13 +19047,13 @@
         <v>2021</v>
       </c>
       <c r="C564" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D564" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E564" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F564" t="s">
         <v>19</v>
@@ -19079,16 +19079,16 @@
         <v>2021</v>
       </c>
       <c r="C565" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D565" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E565" t="s">
         <v>19</v>
       </c>
       <c r="F565" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G565" t="s">
         <v>15</v>
@@ -19111,16 +19111,16 @@
         <v>2021</v>
       </c>
       <c r="C566" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D566" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E566" t="s">
         <v>22</v>
       </c>
       <c r="F566" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G566" t="s">
         <v>15</v>
@@ -19143,13 +19143,13 @@
         <v>2021</v>
       </c>
       <c r="C567" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D567" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E567" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F567" t="s">
         <v>22</v>
@@ -19175,13 +19175,13 @@
         <v>2021</v>
       </c>
       <c r="C568" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D568" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E568" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F568" t="s">
         <v>28</v>
@@ -19207,16 +19207,16 @@
         <v>2021</v>
       </c>
       <c r="C569" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D569" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
       </c>
       <c r="F569" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G569" t="s">
         <v>15</v>
@@ -19239,19 +19239,19 @@
         <v>2021</v>
       </c>
       <c r="C570" t="s">
+        <v>42</v>
+      </c>
+      <c r="D570" t="s">
         <v>46</v>
       </c>
-      <c r="D570" t="s">
+      <c r="E570" t="s">
         <v>50</v>
-      </c>
-      <c r="E570" t="s">
-        <v>42</v>
       </c>
       <c r="F570" t="s">
         <v>22</v>
       </c>
       <c r="G570" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H570">
         <v>23</v>
@@ -19271,19 +19271,19 @@
         <v>2021</v>
       </c>
       <c r="C571" t="s">
+        <v>42</v>
+      </c>
+      <c r="D571" t="s">
         <v>46</v>
-      </c>
-      <c r="D571" t="s">
-        <v>50</v>
       </c>
       <c r="E571" t="s">
         <v>22</v>
       </c>
       <c r="F571" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G571" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H571">
         <v>20</v>
